--- a/technology_surveys/037_real_estate_tech_efficiency_survey--technology_surveys.xlsx
+++ b/technology_surveys/037_real_estate_tech_efficiency_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>team_name</t>
+          <t>software_used</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>team_name</t>
+          <t>Software Used</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>software_used</t>
+          <t>efficiency_rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>software_used</t>
+          <t>Overall Efficiency (1-10)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>email_use</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Email Use (Frequency)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email Frequency (per day)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_use</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone Use (Frequency)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>pain_points</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Pain Points</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_2_section_1</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,64 +727,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_2_section_2</t>
+          <t>ease_of_use</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Ease of Use (1-10)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_2_section_3</t>
+          <t>user_support</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>User Support</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_2_field_1</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Collaboration with Other Teams</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,64 +796,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_2_field_2</t>
+          <t>experience</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Software Experience</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_2_field_3</t>
+          <t>time_spent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Time Spent (minutes per day)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>page_2_field_4</t>
+          <t>reporting_analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Reporting &amp; Analytics</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>page_2_field_5</t>
+          <t>effectiveness</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Overall Effectiveness (1-10)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>page_2_field_6</t>
+          <t>more_likely_to_use</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>More Likely to Use (1-10)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>page_2_field_7</t>
+          <t>software_used_other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Software Used (Other)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>page_2_field_8</t>
+          <t>other_software</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Other Software</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>page_2_field_9</t>
+          <t>other_software_used</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>page 2</t>
+          <t>Other Software Used</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_2_field_10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>page 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_3_section_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>page 3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_3_section_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>page 3</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_3_section_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>page 3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_3_field_1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>page 3</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +1011,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>software_used_choices</t>
+          <t>email_use_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>software_used_choices</t>
+          <t>email_use_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_2_field_3_choices</t>
+          <t>email_use_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_2_field_3_choices</t>
+          <t>email_use_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_2_field_10_choices</t>
+          <t>phone_use_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_2_field_10_choices</t>
+          <t>phone_use_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>phone_use_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>phone_use_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>user_support_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>user_support_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>user_support_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>user_support_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reporting_analytics_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>reporting_analytics_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>reporting_analytics_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>reporting_analytics_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Always</t>
         </is>
       </c>
     </row>
